--- a/public/downloads/packing-list-template.xlsx
+++ b/public/downloads/packing-list-template.xlsx
@@ -226,15 +226,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -629,103 +626,103 @@
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
     </row>
-    <row r="4" ht="25" customHeight="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+    <row r="4" ht="25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6"/>
+      <c r="B5" s="5"/>
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6"/>
+      <c r="B6" s="5"/>
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="6"/>
+      <c r="B7" s="5"/>
     </row>
     <row r="8" ht="25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="6"/>
+      <c r="B8" s="5"/>
     </row>
     <row r="9" ht="25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="6"/>
+      <c r="B9" s="5"/>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="6"/>
+      <c r="B10" s="5"/>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="6"/>
+      <c r="B11" s="5"/>
     </row>
     <row r="12" ht="25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="6"/>
+      <c r="B12" s="5"/>
     </row>
     <row r="13" ht="25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="6"/>
+      <c r="B13" s="5"/>
     </row>
     <row r="14" ht="25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="6"/>
+      <c r="B14" s="5"/>
     </row>
     <row r="15" ht="25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="6"/>
+      <c r="B15" s="5"/>
     </row>
     <row r="16" ht="25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="6"/>
+      <c r="B16" s="5"/>
     </row>
     <row r="17" ht="25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="6"/>
+      <c r="B17" s="5"/>
     </row>
     <row r="18" ht="25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="6"/>
+      <c r="B18" s="5"/>
     </row>
     <row r="19" ht="25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="6"/>
+      <c r="B19" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -758,919 +755,919 @@
     <col min="8" max="13" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" ht="25" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6">
         <f>IFERROR(C2*J2*K2*L2/1000000,0)</f>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7">
         <f>IFERROR(C3*J3*K3*L3/1000000,0)</f>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6">
         <f>IFERROR(C4*J4*K4*L4/1000000,0)</f>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7">
         <f>IFERROR(C5*J5*K5*L5/1000000,0)</f>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6">
         <f>IFERROR(C6*J6*K6*L6/1000000,0)</f>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7">
         <f>IFERROR(C7*J7*K7*L7/1000000,0)</f>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6">
         <f>IFERROR(C8*J8*K8*L8/1000000,0)</f>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7">
         <f>IFERROR(C9*J9*K9*L9/1000000,0)</f>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6">
         <f>IFERROR(C10*J10*K10*L10/1000000,0)</f>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7">
         <f>IFERROR(C11*J11*K11*L11/1000000,0)</f>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6">
         <f>IFERROR(C12*J12*K12*L12/1000000,0)</f>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7">
         <f>IFERROR(C13*J13*K13*L13/1000000,0)</f>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6">
         <f>IFERROR(C14*J14*K14*L14/1000000,0)</f>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7">
         <f>IFERROR(C15*J15*K15*L15/1000000,0)</f>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6">
         <f>IFERROR(C16*J16*K16*L16/1000000,0)</f>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7">
         <f>IFERROR(C17*J17*K17*L17/1000000,0)</f>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6">
         <f>IFERROR(C18*J18*K18*L18/1000000,0)</f>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7">
         <f>IFERROR(C19*J19*K19*L19/1000000,0)</f>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6">
         <f>IFERROR(C20*J20*K20*L20/1000000,0)</f>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7">
         <f>IFERROR(C21*J21*K21*L21/1000000,0)</f>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6">
         <f>IFERROR(C22*J22*K22*L22/1000000,0)</f>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7">
         <f>IFERROR(C23*J23*K23*L23/1000000,0)</f>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6">
         <f>IFERROR(C24*J24*K24*L24/1000000,0)</f>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7">
         <f>IFERROR(C25*J25*K25*L25/1000000,0)</f>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6">
         <f>IFERROR(C26*J26*K26*L26/1000000,0)</f>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7">
         <f>IFERROR(C27*J27*K27*L27/1000000,0)</f>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6">
         <f>IFERROR(C28*J28*K28*L28/1000000,0)</f>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7">
         <f>IFERROR(C29*J29*K29*L29/1000000,0)</f>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6">
         <f>IFERROR(C30*J30*K30*L30/1000000,0)</f>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="8">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7">
         <f>IFERROR(C31*J31*K31*L31/1000000,0)</f>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6">
         <f>IFERROR(C32*J32*K32*L32/1000000,0)</f>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
-      <c r="M33" s="8">
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7">
         <f>IFERROR(C33*J33*K33*L33/1000000,0)</f>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6">
         <f>IFERROR(C34*J34*K34*L34/1000000,0)</f>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8"/>
-      <c r="M35" s="8">
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="7"/>
+      <c r="M35" s="7">
         <f>IFERROR(C35*J35*K35*L35/1000000,0)</f>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="7"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7">
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6">
         <f>IFERROR(C36*J36*K36*L36/1000000,0)</f>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
-      <c r="M37" s="8">
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="7"/>
+      <c r="L37" s="7"/>
+      <c r="M37" s="7">
         <f>IFERROR(C37*J37*K37*L37/1000000,0)</f>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="7"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7">
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6">
         <f>IFERROR(C38*J38*K38*L38/1000000,0)</f>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="8"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="8"/>
-      <c r="L39" s="8"/>
-      <c r="M39" s="8">
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="7"/>
+      <c r="M39" s="7">
         <f>IFERROR(C39*J39*K39*L39/1000000,0)</f>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
-      <c r="J40" s="7"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="7"/>
-      <c r="M40" s="7">
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="6">
         <f>IFERROR(C40*J40*K40*L40/1000000,0)</f>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
-      <c r="I41" s="8"/>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8"/>
-      <c r="L41" s="8"/>
-      <c r="M41" s="8">
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="7"/>
+      <c r="M41" s="7">
         <f>IFERROR(C41*J41*K41*L41/1000000,0)</f>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" s="7"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7"/>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="7">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="6">
         <f>IFERROR(C42*J42*K42*L42/1000000,0)</f>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-      <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="8"/>
-      <c r="M43" s="8">
+      <c r="A43" s="7"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="7"/>
+      <c r="M43" s="7">
         <f>IFERROR(C43*J43*K43*L43/1000000,0)</f>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="7"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="7"/>
-      <c r="K44" s="7"/>
-      <c r="L44" s="7"/>
-      <c r="M44" s="7">
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="6">
         <f>IFERROR(C44*J44*K44*L44/1000000,0)</f>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45" s="8"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="8"/>
-      <c r="M45" s="8">
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="7"/>
+      <c r="M45" s="7">
         <f>IFERROR(C45*J45*K45*L45/1000000,0)</f>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" s="7"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="7"/>
-      <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
-      <c r="M46" s="7">
+      <c r="A46" s="6"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="6"/>
+      <c r="M46" s="6">
         <f>IFERROR(C46*J46*K46*L46/1000000,0)</f>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" s="8"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="8"/>
-      <c r="M47" s="8">
+      <c r="A47" s="7"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="7"/>
+      <c r="M47" s="7">
         <f>IFERROR(C47*J47*K47*L47/1000000,0)</f>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="7"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
-      <c r="L48" s="7"/>
-      <c r="M48" s="7">
+      <c r="A48" s="6"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
+      <c r="M48" s="6">
         <f>IFERROR(C48*J48*K48*L48/1000000,0)</f>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A49" s="8"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
-      <c r="I49" s="8"/>
-      <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="8"/>
-      <c r="M49" s="8">
+      <c r="A49" s="7"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7"/>
+      <c r="M49" s="7">
         <f>IFERROR(C49*J49*K49*L49/1000000,0)</f>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A50" s="7"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="7"/>
-      <c r="K50" s="7"/>
-      <c r="L50" s="7"/>
-      <c r="M50" s="7">
+      <c r="A50" s="6"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="6">
         <f>IFERROR(C50*J50*K50*L50/1000000,0)</f>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A51" s="8"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="8"/>
-      <c r="I51" s="8"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="8"/>
-      <c r="M51" s="8">
+      <c r="A51" s="7"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="7"/>
+      <c r="K51" s="7"/>
+      <c r="L51" s="7"/>
+      <c r="M51" s="7">
         <f>IFERROR(C51*J51*K51*L51/1000000,0)</f>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A52" s="9" t="s">
+      <c r="A52" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B52" s="5"/>
-      <c r="C52" s="9">
+      <c r="B52" s="4"/>
+      <c r="C52" s="8">
         <f>SUM(C2:C51)</f>
       </c>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="9">
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="8">
         <f>SUM(H2:H51)</f>
       </c>
-      <c r="I52" s="9">
+      <c r="I52" s="8">
         <f>SUM(I2:I51)</f>
       </c>
-      <c r="J52" s="5"/>
-      <c r="K52" s="5"/>
-      <c r="L52" s="5"/>
-      <c r="M52" s="9">
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="8">
         <f>SUM(M2:M51)</f>
       </c>
     </row>
@@ -1693,37 +1690,37 @@
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="11" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>37</v>
       </c>
     </row>
